--- a/Python_for_Dev/RE_Text_Processing/fermosa_scrapper/data.xlsx
+++ b/Python_for_Dev/RE_Text_Processing/fermosa_scrapper/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,11 +446,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Combo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Plants</t>
         </is>
       </c>
@@ -473,11 +468,6 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Mini Boncel, Francisii, Silver steel, Kirkii silver blue, Subspicata, Boncel Small Size</t>
         </is>
       </c>
@@ -500,11 +490,6 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>Coppertone, Silver Siam, Silver Princess, Trifaciata Robusta, Fernwood, Gracilis Large</t>
         </is>
       </c>
@@ -527,11 +512,6 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>Cylindrica, Hybrid Delhi, Motomo, Silver Nymph, Gracilis, Tiger</t>
         </is>
       </c>
@@ -554,11 +534,6 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>Coppertone, Fischeri singularis, Kirkii Silver Blue, Midnight Fountain, Hybrid Delhi Large, Francisii</t>
         </is>
       </c>
@@ -581,11 +556,6 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>Kirkii Silver Blue, Patens, Fernwood, Whalefin, Coppertone</t>
         </is>
       </c>
@@ -608,11 +578,6 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>Parva, Lady Charm pup, Cylindrica, Mini Boncel, Francisii, Subspicata</t>
         </is>
       </c>
@@ -635,11 +600,6 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>Silver Nymph, Gracilis, Silver steel, Parva, Subspicata, Crocodile rock</t>
         </is>
       </c>
@@ -662,11 +622,6 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>Cylindrica, Gracilis, Kirkii Silver Blue, Parva, Subspicata, Mini Boncel</t>
         </is>
       </c>
@@ -687,12 +642,7 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,11 +662,6 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>Silver Nymph, Tiger, Moto, Silver Steel, Motomo, Hybrid Delhi</t>
         </is>
       </c>
@@ -739,11 +684,6 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>Dancing Lady; 2, Aff Marsha, Hahnii Gaster</t>
         </is>
       </c>
@@ -764,12 +704,7 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -789,11 +724,6 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t xml:space="preserve">Masoniana Yellow Variegated; 2, Francisii White variegated, Sulcata Yellow Variegated, Boncel Yellow Variegated, </t>
         </is>
       </c>
@@ -816,11 +746,6 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>Cleopatra 2, Sindoro 3, Pagoda4, Silver crown5, Tower6, Midnight fountain 7, Nalika 8, Lobel Kenya 9, Andaman 10, Spoon leaf</t>
         </is>
       </c>
@@ -841,12 +766,7 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -864,12 +784,7 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -889,11 +804,6 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
           <t xml:space="preserve">Sansevieria Pagoda pup, Silver Boncel, Cleopatra, Francisii White Variegated, </t>
         </is>
       </c>
@@ -914,12 +824,7 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -939,11 +844,6 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
           <t>Whitney, Silver Siam</t>
         </is>
       </c>
@@ -966,11 +866,6 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
           <t>Moto, Lady Charm, Gracilis, Crocodile rock, Silver Nymph, Silver Steel</t>
         </is>
       </c>
@@ -991,12 +886,7 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1014,12 +904,7 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1039,11 +924,6 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t xml:space="preserve">Arborescens, Bagamoyensis, Hybrid Delhi, Francisii, </t>
         </is>
       </c>
@@ -1066,11 +946,6 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
           <t>Moto, Mini Boncel, Ballyi, Cylindrica, Hybrid Delhi, Francisii</t>
         </is>
       </c>
@@ -1091,12 +966,7 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1114,12 +984,7 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1137,12 +1002,7 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1162,11 +1022,6 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
           <t>Mini Boncel, Pinguicula, Mini Ballyi</t>
         </is>
       </c>
@@ -1187,12 +1042,7 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1210,12 +1060,7 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1235,11 +1080,6 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
           <t xml:space="preserve">Francisii Yellow Variegated; 2, Francisii Green; 3, Francisii White Variegated, </t>
         </is>
       </c>
@@ -1260,12 +1100,7 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1283,12 +1118,7 @@
           <t>Rs. 599.00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1308,11 +1138,6 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
           <t>Baicularis, Fischeri, Canaliculata</t>
         </is>
       </c>
@@ -1335,11 +1160,6 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
           <t>Subspicata, Moonshine , Superba, Zeylanica , Robusta</t>
         </is>
       </c>
@@ -1360,12 +1180,7 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1383,12 +1198,7 @@
           <t>Rs. 300.00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1406,12 +1216,7 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1429,12 +1234,7 @@
           <t>Rs. 525.00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1454,11 +1254,6 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
           <t>MIDNIGHT FOUNTAIN 2, KATANA, FERNWOOD , UGANDA BLACK , SILVER STEEL , MOTO, SULCATA</t>
         </is>
       </c>
@@ -1479,12 +1274,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1502,12 +1292,7 @@
           <t>Rs. 300.00</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1525,12 +1310,7 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1548,12 +1328,7 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1571,12 +1346,7 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1596,11 +1366,6 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
           <t>Sulcata var, Fern wood, Pearsonii, Fischeri</t>
         </is>
       </c>
@@ -1623,11 +1388,6 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
           <t>Black Gold Compacta; 2, Lake sibaya, Futura Gold</t>
         </is>
       </c>
@@ -1648,12 +1408,7 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1673,11 +1428,6 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
           <t>Jade Marginata</t>
         </is>
       </c>
@@ -1700,11 +1450,6 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
           <t>subspicata 2, Nalika</t>
         </is>
       </c>
@@ -1725,12 +1470,7 @@
           <t>Rs. 5,500.00</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1748,12 +1488,7 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1771,12 +1506,7 @@
           <t>Rs. 1,750.00</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1794,12 +1524,7 @@
           <t>Rs. 550.00</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1817,12 +1542,7 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1840,12 +1560,7 @@
           <t>Rs. 275.00</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1865,11 +1580,6 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
           <t>Gold dust 2, HI Color</t>
         </is>
       </c>
@@ -1893,11 +1603,6 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
           <t>Star dust</t>
         </is>
       </c>
@@ -1918,12 +1623,7 @@
           <t>Rs. 775.00</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1943,11 +1643,6 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
           <t>Pagoda</t>
         </is>
       </c>
@@ -1970,11 +1665,6 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
           <t>Hawaiian Star 2, Patens3, Fischeri4, KATANA</t>
         </is>
       </c>
@@ -1997,11 +1687,6 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
           <t>Ballyi, Mini Ballyi</t>
         </is>
       </c>
@@ -2022,12 +1707,7 @@
           <t>Rs. 3,000.00</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2045,12 +1725,7 @@
           <t>Rs. 8,000.00</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2068,12 +1743,7 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2091,12 +1761,7 @@
           <t>Rs. 1,150.00</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2114,12 +1779,7 @@
           <t>Rs. 1,100.00</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2137,12 +1797,7 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2160,12 +1815,7 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2183,12 +1833,7 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2206,12 +1851,7 @@
           <t>Rs. 2,000.00</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2229,12 +1869,7 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2254,11 +1889,6 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
           <t>Chao Pharya</t>
         </is>
       </c>
@@ -2279,12 +1909,7 @@
           <t>Rs. 999.00</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2304,11 +1929,6 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
           <t>Prima, Prabhu, Jatayu, Tower</t>
         </is>
       </c>
@@ -2331,11 +1951,6 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
           <t>Sulcata var, Fern wood, Pearsonii, Fischeri</t>
         </is>
       </c>
@@ -2358,11 +1973,6 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
           <t>Florida H13 var</t>
         </is>
       </c>
@@ -2385,11 +1995,6 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
           <t>CYLINDRICA  2, BONCEL , UGANDA BLACK , WHALEFINE GREEN, FERNWOOD, COPPERTONE</t>
         </is>
       </c>
@@ -2412,11 +2017,6 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
           <t>Mutant Moonshine</t>
         </is>
       </c>
@@ -2440,11 +2040,6 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
           <t>Robo</t>
         </is>
       </c>
@@ -2467,11 +2062,6 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
           <t>Aslaam</t>
         </is>
       </c>
@@ -2492,12 +2082,7 @@
           <t>Rs. 475.00</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2517,11 +2102,6 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
           <t>Sindoro 2, Silver Boncel 3, Boncel Ming manee</t>
         </is>
       </c>
@@ -2542,12 +2122,7 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2565,12 +2140,7 @@
           <t>Rs. 1,300.00</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2588,12 +2158,7 @@
           <t>Rs. 2,750.00</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2611,12 +2176,7 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2634,12 +2194,7 @@
           <t>Rs. 275.00</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2657,12 +2212,7 @@
           <t>Rs. 275.00</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2680,12 +2230,7 @@
           <t>Rs. 800.00</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2703,12 +2248,7 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2726,12 +2266,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2749,12 +2284,7 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2772,12 +2302,7 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2795,12 +2320,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2818,12 +2338,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2841,12 +2356,7 @@
           <t>Rs. 500.00</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2864,12 +2374,7 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2889,11 +2394,6 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
           <t>Parbhu</t>
         </is>
       </c>
@@ -2914,12 +2414,7 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2939,11 +2434,6 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
           <t>BAO DAM</t>
         </is>
       </c>
@@ -2964,12 +2454,7 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2988,12 +2473,7 @@
       Rs. 1,599.00</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3011,12 +2491,7 @@
           <t>Rs. 2,299.00</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3035,12 +2510,7 @@
       Rs. 1,650.00</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3058,12 +2528,7 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3083,11 +2548,6 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
           <t>Green Arrow, Black Gold compacta, Nelsonii banded</t>
         </is>
       </c>
@@ -3110,11 +2570,6 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
           <t>STAR DUST, SENGUKUNI, RAVANA, PHANPHET</t>
         </is>
       </c>
@@ -3137,11 +2592,6 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
           <t>Florida H13 var</t>
         </is>
       </c>
@@ -3164,11 +2614,6 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
           <t>Aswathama</t>
         </is>
       </c>
@@ -3191,11 +2636,6 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
           <t>ERYTHERAE, FISCHERI , PATENS, SULCATA, B10, MIDNIGHT FOUNTAIN</t>
         </is>
       </c>
@@ -3216,12 +2656,7 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3241,11 +2676,6 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
           <t>BAO DAM</t>
         </is>
       </c>
@@ -3268,11 +2698,6 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
           <t>Sawasdee</t>
         </is>
       </c>
@@ -3293,12 +2718,7 @@
           <t>Rs. 575.00</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3316,12 +2736,7 @@
           <t>Rs. 1,499.00</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3339,12 +2754,7 @@
           <t>Rs. 1,799.00</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3362,12 +2772,7 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3385,12 +2790,7 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3410,11 +2810,6 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
           <t>Sheila</t>
         </is>
       </c>
@@ -3437,11 +2832,6 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
           <t>Robo</t>
         </is>
       </c>
@@ -3464,11 +2854,6 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
           <t xml:space="preserve">Sinta (named on Mata Seeta of Ramayana, In Indonesia SEETA is spelt as SINTA), </t>
         </is>
       </c>
@@ -3489,12 +2874,7 @@
           <t>Rs. 575.00</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3514,11 +2894,6 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
           <t>Black Ants</t>
         </is>
       </c>
@@ -3539,12 +2914,7 @@
           <t>Rs. 1,650.00</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3562,12 +2932,7 @@
           <t>Rs. 1,950.00</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3585,12 +2950,7 @@
           <t>Rs. 1,350.00</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3608,12 +2968,7 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3631,12 +2986,7 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3654,12 +3004,7 @@
           <t>Rs. 799.00</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3677,12 +3022,7 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3700,12 +3040,7 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3723,12 +3058,7 @@
           <t>Rs. 1,500.00</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3746,12 +3076,7 @@
           <t>Rs. 999.00</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3771,11 +3096,6 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
           <t>Black ants 2, Silver BoncelIncluding shipping</t>
         </is>
       </c>
@@ -3796,12 +3116,7 @@
           <t>Rs. 1,100.00</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3819,12 +3134,7 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3842,12 +3152,7 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3865,12 +3170,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3888,12 +3188,7 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3911,12 +3206,7 @@
           <t>Rs. 1,100.00</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3934,12 +3224,7 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3957,12 +3242,7 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3980,12 +3260,7 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4003,12 +3278,7 @@
           <t>Rs. 2,000.00</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4026,12 +3296,7 @@
           <t>Rs. 1,000.00</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4049,12 +3314,7 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4072,12 +3332,7 @@
           <t>Rs. 1,499.00</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4095,12 +3350,7 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4118,12 +3368,7 @@
           <t>Rs. 1,650.00</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4141,12 +3386,7 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4164,12 +3404,7 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4187,12 +3422,7 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4210,12 +3440,7 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4233,12 +3458,7 @@
           <t>Rs. 5,000.00</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4256,12 +3476,7 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4279,12 +3494,7 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4302,12 +3512,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4325,12 +3530,7 @@
           <t>Rs. 1,850.00</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4348,12 +3548,7 @@
           <t>Rs. 1,450.00</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4371,12 +3566,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4394,12 +3584,7 @@
           <t>Rs. 1,150.00</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4417,12 +3602,7 @@
           <t>Rs. 1,750.00</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4440,12 +3620,7 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4463,12 +3638,7 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4486,12 +3656,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4509,12 +3674,7 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4532,12 +3692,7 @@
           <t>Rs. 1,750.00</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Python_for_Dev/RE_Text_Processing/fermosa_scrapper/data.xlsx
+++ b/Python_for_Dev/RE_Text_Processing/fermosa_scrapper/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,62 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Plants</t>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Variegated</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_6</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_7</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_8</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_9</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Plant_10</t>
         </is>
       </c>
     </row>
@@ -468,9 +523,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mini Boncel, Francisii, Silver steel, Kirkii silver blue, Subspicata, Boncel Small Size</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mini Boncel</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Francisii</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Silver steel</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Kirkii silver blue</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Subspicata</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Boncel Small Size</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,9 +584,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Coppertone, Silver Siam, Silver Princess, Trifaciata Robusta, Fernwood, Gracilis Large</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Coppertone</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Silver Siam</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Silver Princess</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Trifaciata Robusta</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fernwood</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Gracilis Large</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,9 +645,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cylindrica, Hybrid Delhi, Motomo, Silver Nymph, Gracilis, Tiger</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cylindrica</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hybrid Delhi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Motomo</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Silver Nymph</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Gracilis</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tiger</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -534,9 +706,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Coppertone, Fischeri singularis, Kirkii Silver Blue, Midnight Fountain, Hybrid Delhi Large, Francisii</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Coppertone</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fischeri singularis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kirkii Silver Blue</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Midnight Fountain</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hybrid Delhi Large</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Francisii</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -556,9 +767,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kirkii Silver Blue, Patens, Fernwood, Whalefin, Coppertone</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kirkii Silver Blue</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Patens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fernwood</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Whalefin</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Coppertone</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -578,9 +824,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Parva, Lady Charm pup, Cylindrica, Mini Boncel, Francisii, Subspicata</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Parva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lady Charm pup</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Cylindrica</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mini Boncel</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Francisii</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Subspicata</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -600,9 +885,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Silver Nymph, Gracilis, Silver steel, Parva, Subspicata, Crocodile rock</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Silver Nymph</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gracilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Silver steel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Parva</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Subspicata</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Crocodile rock</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,9 +946,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cylindrica, Gracilis, Kirkii Silver Blue, Parva, Subspicata, Mini Boncel</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cylindrica</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gracilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kirkii Silver Blue</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Parva</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Subspicata</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Mini Boncel</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,7 +1005,26 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,9 +1044,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Silver Nymph, Tiger, Moto, Silver Steel, Motomo, Hybrid Delhi</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Silver Nymph</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tiger</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Moto</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Silver Steel</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Motomo</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Hybrid Delhi</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -684,9 +1105,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dancing Lady; 2, Aff Marsha, Hahnii Gaster</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dancing Lady</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Aff Marsha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hahnii Gaster</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -704,7 +1152,26 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -724,9 +1191,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masoniana Yellow Variegated; 2, Francisii White variegated, Sulcata Yellow Variegated, Boncel Yellow Variegated, </t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Masoniana Yellow Variegated</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Francisii White variegated</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sulcata Yellow Variegated</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Boncel Yellow Variegated</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -746,7 +1244,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cleopatra 2, Sindoro 3, Pagoda4, Silver crown5, Tower6, Midnight fountain 7, Nalika 8, Lobel Kenya 9, Andaman 10, Spoon leaf</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cleopatra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sindoro</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pagoda</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Silver crown</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Tower</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Midnight fountain</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Nalika</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Lobel Kenya</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Andaman</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Spoon leaf</t>
         </is>
       </c>
     </row>
@@ -766,7 +1319,26 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -784,7 +1356,26 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -804,9 +1395,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sansevieria Pagoda pup, Silver Boncel, Cleopatra, Francisii White Variegated, </t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sansevieria Pagoda pup</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver Boncel</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Cleopatra</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Francisii White Variegated</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -824,7 +1446,26 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -844,9 +1485,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Whitney, Silver Siam</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Whitney</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Silver Siam</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -866,9 +1530,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Moto, Lady Charm, Gracilis, Crocodile rock, Silver Nymph, Silver Steel</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Moto</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lady Charm</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Gracilis</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Crocodile rock</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Silver Nymph</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Silver Steel</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -886,7 +1589,26 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -904,7 +1626,26 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -924,9 +1665,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arborescens, Bagamoyensis, Hybrid Delhi, Francisii, </t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Arborescens</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bagamoyensis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hybrid Delhi</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Francisii</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -946,9 +1718,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Moto, Mini Boncel, Ballyi, Cylindrica, Hybrid Delhi, Francisii</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Moto</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Mini Boncel</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ballyi</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Cylindrica</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Hybrid Delhi</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Francisii</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -966,7 +1777,26 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -984,7 +1814,26 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,7 +1851,26 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,9 +1890,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mini Boncel, Pinguicula, Mini Ballyi</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mini Boncel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pinguicula</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Mini Ballyi</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,7 +1937,26 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1060,7 +1974,26 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1080,9 +2013,36 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisii Yellow Variegated; 2, Francisii Green; 3, Francisii White Variegated, </t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Francisii Yellow Variegated</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Francisii Green</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Francisii White Variegated</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1100,7 +2060,26 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1118,7 +2097,26 @@
           <t>Rs. 599.00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1138,9 +2136,36 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Baicularis, Fischeri, Canaliculata</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Baicularis</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fischeri</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Canaliculata</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1160,9 +2185,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Subspicata, Moonshine , Superba, Zeylanica , Robusta</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Subspicata</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Moonshine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Superba</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Zeylanica</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Robusta</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1180,7 +2240,26 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1198,7 +2277,26 @@
           <t>Rs. 300.00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1216,7 +2314,26 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1234,7 +2351,26 @@
           <t>Rs. 525.00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1254,9 +2390,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MIDNIGHT FOUNTAIN 2, KATANA, FERNWOOD , UGANDA BLACK , SILVER STEEL , MOTO, SULCATA</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MIDNIGHT FOUNTAIN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>KATANA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>FERNWOOD</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>UGANDA BLACK</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>SILVER STEEL</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>MOTO</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>SULCATA</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1274,7 +2453,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1292,7 +2490,26 @@
           <t>Rs. 300.00</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1310,7 +2527,26 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1328,7 +2564,26 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1346,7 +2601,26 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1366,9 +2640,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sulcata var, Fern wood, Pearsonii, Fischeri</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Sulcata var</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Fern wood</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Pearsonii</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Fischeri</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1388,9 +2693,36 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Black Gold Compacta; 2, Lake sibaya, Futura Gold</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Black Gold Compacta</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lake sibaya</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Futura Gold</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1408,7 +2740,26 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1428,9 +2779,44 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Jade Marginata</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Golden Hahnii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Twisted Sisters</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Night Owl</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Black Jade</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1450,9 +2836,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>subspicata 2, Nalika</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>subspicata</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nalika</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1470,7 +2879,26 @@
           <t>Rs. 5,500.00</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1488,7 +2916,26 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1506,7 +2953,26 @@
           <t>Rs. 1,750.00</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1524,7 +2990,26 @@
           <t>Rs. 550.00</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1542,7 +3027,26 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1560,7 +3064,26 @@
           <t>Rs. 275.00</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1580,9 +3103,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Gold dust 2, HI Color</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gold dust</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HI Color</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1603,9 +3149,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Star dust</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phanphet</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Tower</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Ravana</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1623,7 +3200,26 @@
           <t>Rs. 775.00</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1643,9 +3239,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Pagoda</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nalika</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Fighter</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sweet celery</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Tower</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Lobel Kenya</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Sindoro  Rs</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1665,9 +3304,40 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Hawaiian Star 2, Patens3, Fischeri4, KATANA</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Hawaiian Star</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Patens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Fischeri</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>KATANA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1687,9 +3357,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ballyi, Mini Ballyi</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ballyi</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Mini Ballyi</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1707,7 +3400,26 @@
           <t>Rs. 3,000.00</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1725,7 +3437,26 @@
           <t>Rs. 8,000.00</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1743,7 +3474,26 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1761,7 +3511,26 @@
           <t>Rs. 1,150.00</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1779,7 +3548,26 @@
           <t>Rs. 1,100.00</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1797,7 +3585,26 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1815,7 +3622,26 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1833,7 +3659,26 @@
           <t>Rs. 450.00</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1851,7 +3696,26 @@
           <t>Rs. 2,000.00</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1869,7 +3733,26 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1889,9 +3772,36 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>Chao Pharya</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Benthieng</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Nakhon luang</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1909,7 +3819,26 @@
           <t>Rs. 999.00</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1929,9 +3858,40 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Prima, Prabhu, Jatayu, Tower</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Jatayu</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Tower</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1951,9 +3911,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sulcata var, Fern wood, Pearsonii, Fischeri</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sulcata var</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fern wood</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Pearsonii</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Fischeri</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1973,9 +3964,52 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Florida H13 var</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Florida H   var</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Uganda black var</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Fernwood var</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sulcata var</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Stella var  Images are for reference purposes only</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Actual product may vary in shape or appearance based on climate  age  height  etc</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Please Note  Succulents change colour throughout the year and the plants we deliver can sometimes look different from the pictures</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1995,9 +4029,48 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CYLINDRICA  2, BONCEL , UGANDA BLACK , WHALEFINE GREEN, FERNWOOD, COPPERTONE</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CYLINDRICA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>BONCEL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>UGANDA BLACK</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>WHALEFINE GREEN</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>FERNWOOD</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>COPPERTONE</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2017,9 +4090,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Mutant Moonshine</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Moonshine Variegated</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Alslaam</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Black Sword aka Green Arrow</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Nelsonni banded   All are hardy variety which are easy to maintain</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2040,9 +4148,52 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Robo</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Boncel var</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Platinum cross</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Marsha anjani</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Fighter</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Nilin</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Silver boncel  One of the most popular combos by Fermosa Plants</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2062,9 +4213,44 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Aslaam</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Moonshine mutant</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Nelsonii banded</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Green arrow</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Moonshine var    Rs</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2082,7 +4268,26 @@
           <t>Rs. 475.00</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2102,9 +4307,36 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sindoro 2, Silver Boncel 3, Boncel Ming manee</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sindoro</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Silver Boncel</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Boncel Ming manee</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2122,7 +4354,26 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2140,7 +4391,26 @@
           <t>Rs. 1,300.00</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2158,7 +4428,26 @@
           <t>Rs. 2,750.00</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2176,7 +4465,26 @@
           <t>Rs. 199.00</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2194,7 +4502,26 @@
           <t>Rs. 275.00</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2212,7 +4539,26 @@
           <t>Rs. 275.00</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2230,7 +4576,26 @@
           <t>Rs. 800.00</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2248,7 +4613,26 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2266,7 +4650,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2284,7 +4687,26 @@
           <t>Rs. 299.00</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2302,7 +4724,26 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2320,7 +4761,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2338,7 +4798,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2356,7 +4835,26 @@
           <t>Rs. 500.00</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2374,7 +4872,26 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2394,9 +4911,48 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Parbhu</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Sindoro</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Jatayu</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Lady charm</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Kitonga</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2414,7 +4970,26 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2434,9 +5009,44 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>BAO DAM</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ADVENTUS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>BLACK ANTS</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>JATAYU</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>BLACK MLANDI</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2454,7 +5064,26 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2473,7 +5102,26 @@
       Rs. 1,599.00</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2491,7 +5139,26 @@
           <t>Rs. 2,299.00</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2510,7 +5177,26 @@
       Rs. 1,650.00</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2528,7 +5214,26 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2548,9 +5253,36 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Green Arrow, Black Gold compacta, Nelsonii banded</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Green Arrow</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Black Gold compacta</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Nelsonii banded</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2570,9 +5302,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>STAR DUST, SENGUKUNI, RAVANA, PHANPHET</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>STAR DUST</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SENGUKUNI</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>RAVANA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>PHANPHET</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2592,9 +5355,52 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Florida H13 var</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Florida H   var</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Uganda black var</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Fernwood var</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Sulcata var</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Stella var  Images are for reference purposes only</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Actual product may vary in shape or appearance based on climate  age  height  etc</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Please Note  Succulents change colour throughout the year and the plants we deliver can sometimes look different from the pictures</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2614,9 +5420,60 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>Aswathama</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Sri Rama</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sinta named on Goddness Seeta of Ramayana</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Jatayu</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Ravana ex Thailand</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Rahwana ex Indonesia and that s how Ravana is spelled there</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Both Ravana of Thai origin and Rahwana ex Indonesia have completely different characteristics</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Sengkuni or Shakuni of Mahabharatha</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2636,9 +5493,48 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ERYTHERAE, FISCHERI , PATENS, SULCATA, B10, MIDNIGHT FOUNTAIN</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ERYTHERAE</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>FISCHERI</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>PATENS</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SULCATA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>MIDNIGHT FOUNTAIN</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2656,7 +5552,26 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2676,9 +5591,44 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>BAO DAM</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ADVENTUS</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>BLACK ANTS</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>JATAYU</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>BLACK MLANDI</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2698,9 +5648,40 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>Sawasdee</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Robo</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Platinum cross</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Sindoro</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2718,7 +5699,26 @@
           <t>Rs. 575.00</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2736,7 +5736,26 @@
           <t>Rs. 1,499.00</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2754,7 +5773,26 @@
           <t>Rs. 1,799.00</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2772,7 +5810,26 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2790,7 +5847,26 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2810,9 +5886,40 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>Sheila</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Adventus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Rahwana</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2832,9 +5939,40 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>Robo</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bao dam</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Star gate</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2854,9 +5992,32 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sinta (named on Mata Seeta of Ramayana, In Indonesia SEETA is spelt as SINTA), </t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Sinta  named on Mata Seeta of Ramayana</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>In Indonesia SEETA is spelt as SINTA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2874,7 +6035,26 @@
           <t>Rs. 575.00</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2894,9 +6074,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>Black Ants</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Nelsonii banded</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Black Gold compacta</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Green arrow</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Moonshine mutant</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2914,7 +6129,26 @@
           <t>Rs. 1,650.00</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2932,7 +6166,26 @@
           <t>Rs. 1,950.00</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2950,7 +6203,26 @@
           <t>Rs. 1,350.00</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2968,7 +6240,26 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2986,7 +6277,26 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3004,7 +6314,26 @@
           <t>Rs. 799.00</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3022,7 +6351,26 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3040,7 +6388,26 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3058,7 +6425,26 @@
           <t>Rs. 1,500.00</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3076,7 +6462,26 @@
           <t>Rs. 999.00</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3096,9 +6501,32 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Black ants 2, Silver BoncelIncluding shipping</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Not Eligible</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Black ants</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Silver BoncelIncluding shipping</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3116,7 +6544,26 @@
           <t>Rs. 1,100.00</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3134,7 +6581,26 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3152,7 +6618,26 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3170,7 +6655,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3188,7 +6692,26 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3206,7 +6729,26 @@
           <t>Rs. 1,100.00</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3224,7 +6766,26 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3242,7 +6803,26 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3260,7 +6840,26 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3278,7 +6877,26 @@
           <t>Rs. 2,000.00</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3296,7 +6914,26 @@
           <t>Rs. 1,000.00</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3314,7 +6951,26 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3332,7 +6988,26 @@
           <t>Rs. 1,499.00</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3350,7 +7025,26 @@
           <t>Rs. 499.00</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3368,7 +7062,26 @@
           <t>Rs. 1,650.00</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3386,7 +7099,26 @@
           <t>Rs. 250.00</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3404,7 +7136,26 @@
           <t>Rs. 650.00</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3422,7 +7173,26 @@
           <t>Rs. 699.00</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3440,7 +7210,26 @@
           <t>Rs. 350.00</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3458,7 +7247,26 @@
           <t>Rs. 5,000.00</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3476,7 +7284,26 @@
           <t>Rs. 600.00</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3494,7 +7321,26 @@
           <t>Rs. 750.00</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3512,7 +7358,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3530,7 +7395,26 @@
           <t>Rs. 1,850.00</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3548,7 +7432,26 @@
           <t>Rs. 1,450.00</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3566,7 +7469,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3584,7 +7506,26 @@
           <t>Rs. 1,150.00</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3602,7 +7543,26 @@
           <t>Rs. 1,750.00</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3620,7 +7580,26 @@
           <t>Rs. 1,250.00</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3638,7 +7617,26 @@
           <t>Rs. 3,500.00</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3656,7 +7654,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3674,7 +7691,26 @@
           <t>Rs. 850.00</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3692,7 +7728,26 @@
           <t>Rs. 1,750.00</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
